--- a/results/results_tables.xlsx
+++ b/results/results_tables.xlsx
@@ -472,13 +472,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03067017571398636</v>
+        <v>0.0443690480230467</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07588133172119592</v>
+        <v>0.1139713581881778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7042034477311765</v>
+        <v>0.7687743159934843</v>
       </c>
       <c r="E3" t="n">
         <v>456</v>
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004564885383117848</v>
+        <v>0.007747756392249174</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01740515849566459</v>
+        <v>0.02669679326937849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7744744040073978</v>
+        <v>0.7402517099043628</v>
       </c>
       <c r="E4" t="n">
         <v>456</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04419245229420252</v>
+        <v>0.02726368706987225</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1082049855281965</v>
+        <v>0.08013990713110179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6886321275529541</v>
+        <v>0.6925173521115918</v>
       </c>
       <c r="E5" t="n">
         <v>456</v>
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01015854868251101</v>
+        <v>0.0290520676428805</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03721848736882839</v>
+        <v>0.08255285088535151</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7711195776090879</v>
+        <v>0.6969526845707346</v>
       </c>
       <c r="E6" t="n">
         <v>456</v>
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0308008938732273</v>
+        <v>0.04506025782888396</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07550793357030532</v>
+        <v>0.1182376907955529</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7443445165705991</v>
+        <v>0.8159305254064575</v>
       </c>
       <c r="E7" t="n">
         <v>456</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03133046797055632</v>
+        <v>0.03955872382751933</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07665727069927911</v>
+        <v>0.1091805110869532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8735338303448266</v>
+        <v>0.9113571434732218</v>
       </c>
       <c r="E8" t="n">
         <v>456</v>
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0312006676749899</v>
+        <v>0.03385725800671752</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07519265222229291</v>
+        <v>0.09753615575448335</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9162407448016395</v>
+        <v>0.9508665543321618</v>
       </c>
       <c r="E9" t="n">
         <v>456</v>
@@ -654,13 +654,13 @@
         <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0308008938732273</v>
+        <v>0.04506025782888396</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07550793357030532</v>
+        <v>0.1182376907955529</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7443445165705991</v>
+        <v>0.8159305254064575</v>
       </c>
       <c r="F2" t="n">
         <v>456</v>
@@ -676,13 +676,13 @@
         <v>0.4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03133046797055632</v>
+        <v>0.03955872382751933</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07665727069927911</v>
+        <v>0.1091805110869532</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8735338303448266</v>
+        <v>0.9113571434732218</v>
       </c>
       <c r="F3" t="n">
         <v>456</v>
@@ -698,13 +698,13 @@
         <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0312006676749899</v>
+        <v>0.03385725800671752</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07519265222229291</v>
+        <v>0.09753615575448335</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9162407448016395</v>
+        <v>0.9508665543321618</v>
       </c>
       <c r="F4" t="n">
         <v>456</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9162407448016395</v>
+        <v>0.9508665543321618</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +838,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>session_1_mf_rho_0.2</t>
+          <t>session_1_mf_rho_0.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -847,15 +847,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.1074</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -864,7 +864,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>session_2_mf_rho_0.5</t>
+          <t>session_2_mf_rho_0.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2787</v>
+        <v>0.3015</v>
       </c>
     </row>
     <row r="4">
@@ -890,7 +890,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>session_3_genre_rho_0.4</t>
+          <t>session_3_genre_rho_0.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1867</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="5">
@@ -916,7 +916,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>session_1_mf_rho_0.2</t>
+          <t>session_1_mf_rho_0.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -925,15 +925,15 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1481</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="6">
@@ -942,7 +942,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>session_2_mf_rho_0.5</t>
+          <t>session_2_mf_rho_0.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,15 +951,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.3727</v>
+        <v>0.2905</v>
       </c>
     </row>
     <row r="7">
@@ -968,7 +968,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>session_3_genre_rho_0.4</t>
+          <t>session_3_genre_rho_0.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -977,15 +977,15 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.217</v>
+        <v>0.1724</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>session_1_mf_rho_0.2</t>
+          <t>session_1_mf_rho_0.1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1003,15 +1003,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.1318</v>
+        <v>0.0902</v>
       </c>
     </row>
     <row r="9">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>session_2_mf_rho_0.5</t>
+          <t>session_2_mf_rho_0.3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1029,15 +1029,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3037</v>
+        <v>0.2774</v>
       </c>
     </row>
     <row r="10">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>session_3_genre_rho_0.4</t>
+          <t>session_3_genre_rho_0.3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1304</v>
+        <v>0.1084</v>
       </c>
     </row>
   </sheetData>

--- a/results/results_tables.xlsx
+++ b/results/results_tables.xlsx
@@ -453,16 +453,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1180096797899421</v>
+        <v>0.1372484839888691</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2450737726080048</v>
+        <v>0.1763793896959072</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7655742528922279</v>
+        <v>0.7516514852131387</v>
       </c>
       <c r="E2" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3">
@@ -472,16 +472,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0443690480230467</v>
+        <v>0.04227655000251854</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1139713581881778</v>
+        <v>0.0687804064206954</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7687743159934843</v>
+        <v>0.769627819404332</v>
       </c>
       <c r="E3" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4">
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007747756392249174</v>
+        <v>0.008455548685976855</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02669679326937849</v>
+        <v>0.01641484789877395</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7402517099043628</v>
+        <v>0.7445750748005838</v>
       </c>
       <c r="E4" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5">
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02726368706987225</v>
+        <v>0.03093102849764791</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08013990713110179</v>
+        <v>0.05119444723823299</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6925173521115918</v>
+        <v>0.6939375629410139</v>
       </c>
       <c r="E5" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0290520676428805</v>
+        <v>0.03155433697328023</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08255285088535151</v>
+        <v>0.05172057393767405</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6969526845707346</v>
+        <v>0.6983660301669868</v>
       </c>
       <c r="E6" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7">
@@ -548,16 +548,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04506025782888396</v>
+        <v>0.0415912373929907</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1182376907955529</v>
+        <v>0.07044519694761042</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8159305254064575</v>
+        <v>0.8135765638046615</v>
       </c>
       <c r="E7" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8">
@@ -567,16 +567,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03955872382751933</v>
+        <v>0.03969973590404352</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1091805110869532</v>
+        <v>0.06808766814498235</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9113571434732218</v>
+        <v>0.9061973245006737</v>
       </c>
       <c r="E8" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9">
@@ -586,16 +586,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03385725800671752</v>
+        <v>0.03947045139940039</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09753615575448335</v>
+        <v>0.06647934642121738</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9508665543321618</v>
+        <v>0.9306102499791871</v>
       </c>
       <c r="E9" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -654,16 +654,16 @@
         <v>0.1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04506025782888396</v>
+        <v>0.0415912373929907</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1182376907955529</v>
+        <v>0.07044519694761042</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8159305254064575</v>
+        <v>0.8135765638046615</v>
       </c>
       <c r="F2" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3">
@@ -676,16 +676,16 @@
         <v>0.4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03955872382751933</v>
+        <v>0.03969973590404352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1091805110869532</v>
+        <v>0.06808766814498235</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9113571434732218</v>
+        <v>0.9061973245006737</v>
       </c>
       <c r="F3" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4">
@@ -698,16 +698,16 @@
         <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03385725800671752</v>
+        <v>0.03947045139940039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09753615575448335</v>
+        <v>0.06647934642121738</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9508665543321618</v>
+        <v>0.9306102499791871</v>
       </c>
       <c r="F4" t="n">
-        <v>456</v>
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1180096797899421</v>
+        <v>0.1372484839888691</v>
       </c>
     </row>
     <row r="3">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2450737726080048</v>
+        <v>0.1763793896959072</v>
       </c>
     </row>
     <row r="4">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9508665543321618</v>
+        <v>0.9306102499791871</v>
       </c>
     </row>
   </sheetData>
@@ -851,11 +851,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="3">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.3015</v>
+        <v>0.3006</v>
       </c>
     </row>
     <row r="4">
@@ -903,11 +903,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.1148</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="5">
@@ -929,11 +929,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.0895</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="6">
@@ -955,11 +955,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>3/10</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.2905</v>
+        <v>0.2968</v>
       </c>
     </row>
     <row r="7">
@@ -981,11 +981,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>10/10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.1724</v>
+        <v>0.1607</v>
       </c>
     </row>
     <row r="8">
@@ -1007,11 +1007,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.0902</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1059,11 +1059,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10/10</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.1084</v>
+        <v>0.1037</v>
       </c>
     </row>
   </sheetData>
